--- a/output/pdf_financials_xlsx/PEMC.xlsx
+++ b/output/pdf_financials_xlsx/PEMC.xlsx
@@ -3598,31 +3598,31 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.020126</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.29244</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.35889</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.419043</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.653666</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.683934</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.410619</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.09699000000000001</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.265965</v>
       </c>
     </row>
     <row r="93">
@@ -6273,7 +6273,11 @@
           <t>Reserves (Note 12)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -10972,7 +10976,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E101" s="5" t="n">
         <v>0.020126</v>
       </c>

--- a/output/pdf_financials_xlsx/PEMC.xlsx
+++ b/output/pdf_financials_xlsx/PEMC.xlsx
@@ -789,13 +789,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.000348</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000395</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.000552</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1343,13 +1343,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.298264</v>
+        <v>-0.298612</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.654079</v>
+        <v>-0.654474</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.031259</v>
+        <v>-1.031811</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.011754</v>
@@ -1411,13 +1411,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.298264</v>
+        <v>-0.298612</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.654079</v>
+        <v>-0.654474</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.031259</v>
+        <v>-1.031811</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.011754</v>
@@ -1590,31 +1590,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.425478</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.493234</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.204491</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.014286</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.435315</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.097135</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.313539</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.256913</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.188347</v>
       </c>
     </row>
     <row r="35">
@@ -1658,31 +1658,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.002333</v>
+        <v>0.427811</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.001711</v>
+        <v>1.494945</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.091694</v>
+        <v>0.296185</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.235122</v>
+        <v>0.249408</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.09686</v>
+        <v>0.532175</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.140458</v>
+        <v>1.237593</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.069024</v>
+        <v>0.382563</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.07044499999999999</v>
+        <v>0.327358</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.046074</v>
+        <v>0.234421</v>
       </c>
     </row>
     <row r="37">
@@ -2066,31 +2066,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.425478</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.507765</v>
+        <v>0.014531</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.307896</v>
+        <v>0.103405</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.148832</v>
+        <v>0.134546</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.768966</v>
+        <v>0.333651</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.162046</v>
+        <v>0.064911</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.336067</v>
+        <v>0.022528</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.319385</v>
+        <v>0.062472</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.253767</v>
+        <v>0.06542000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5607,7 +5607,11 @@
           <t>Reclamation deposits (Note 7)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -6705,7 +6709,11 @@
           <t>Reclamation deposits (Note 7)</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -10004,7 +10012,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
@@ -10488,7 +10496,11 @@
           <t>Reclamation deposits (Note 7)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E93" s="5" t="n">
         <v>0.027</v>
       </c>
@@ -16181,7 +16193,11 @@
           <t>Purchase of reclamation deposits</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E190" s="5" t="n">
         <v>-0.002</v>
       </c>
@@ -16830,7 +16846,11 @@
           <t>Purchase of reclamation deposits</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -20589,7 +20609,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E268" s="5" t="n">

--- a/output/pdf_financials_xlsx/PEMC.xlsx
+++ b/output/pdf_financials_xlsx/PEMC.xlsx
@@ -628,22 +628,22 @@
         <v>0.255672</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.113955</v>
+        <v>0.244055</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.090118</v>
+        <v>0.242193</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.09077499999999999</v>
+        <v>0.267433</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.09</v>
+        <v>0.292231</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.09</v>
+        <v>0.323</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.09</v>
+        <v>0.397</v>
       </c>
     </row>
     <row r="8">
@@ -730,22 +730,22 @@
         <v>0.255672</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.113955</v>
+        <v>0.244055</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.090118</v>
+        <v>0.242193</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.09077499999999999</v>
+        <v>0.267433</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.09</v>
+        <v>0.292231</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.09</v>
+        <v>0.323</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.09</v>
+        <v>0.397</v>
       </c>
     </row>
     <row r="11">
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006623</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.130081</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>-0.217778</v>
@@ -4365,13 +4365,13 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.638317</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.025463</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.043442</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006623</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.130081</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>-0.217778</v>
@@ -5051,10 +5051,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.265703</v>
+        <v>-0.272326</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.487217</v>
+        <v>-0.617298</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-1.40883</v>
@@ -14876,7 +14876,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E167" t="inlineStr">
         <is>
           <t>-</t>
@@ -16012,7 +16016,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -16720,7 +16728,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -17326,7 +17338,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E209" s="5" t="n">
         <v>-0.006623</v>
       </c>
@@ -17907,7 +17923,11 @@
           <t>Consulting and directors fees (Note 10)</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
